--- a/DeltaStream_Attribution_Agent_Sample_Output.xlsx
+++ b/DeltaStream_Attribution_Agent_Sample_Output.xlsx
@@ -2355,7 +2355,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Source APIs -&gt; Kafka -&gt; DeltaStream (identity resolution) -&gt; ClickHouse -&gt; Agent -&gt; this workbook</t>
+          <t>Source APIs -&gt; Kafka (Confluent Cloud) -&gt; DeltaStream (identity resolution + materialized views) -&gt; MCP -&gt; Agent -&gt; this workbook</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Attribution views refresh every 15 minutes; board pack generated weekly</t>
+          <t>DeltaStream materialized views update continuously; board pack generated weekly</t>
         </is>
       </c>
     </row>
